--- a/data/trans_orig/IP05A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83042</t>
+          <t>83616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101131</t>
+          <t>102391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91568</t>
+          <t>90940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110340</t>
+          <t>110801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180073</t>
+          <t>180430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207635</t>
+          <t>207579</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32223</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49723</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54859</t>
+          <t>54761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72324</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99081</t>
+          <t>98340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22568</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>102089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125121</t>
+          <t>124312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>109946</t>
+          <t>110610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>134858</t>
+          <t>135676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219436</t>
+          <t>219347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>253358</t>
+          <t>252637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64568</t>
+          <t>64863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85747</t>
+          <t>86080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>70702</t>
+          <t>70013</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94591</t>
+          <t>95416</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>142900</t>
+          <t>140426</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>175905</t>
+          <t>173003</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>24462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26229</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46933</t>
+          <t>45719</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79810</t>
+          <t>80599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>100154</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77204</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>97675</t>
+          <t>98165</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>165181</t>
+          <t>164868</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192285</t>
+          <t>192527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37631</t>
+          <t>36193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55686</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>47561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66887</t>
+          <t>66531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>89797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115111</t>
+          <t>115730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>25614</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>15938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29587</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>32014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51167</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72271</t>
+          <t>72214</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96068</t>
+          <t>97790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73520</t>
+          <t>73936</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96964</t>
+          <t>97192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>152670</t>
+          <t>151796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>187929</t>
+          <t>185610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71165</t>
+          <t>68600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93719</t>
+          <t>93261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65343</t>
+          <t>65616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88491</t>
+          <t>88692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140068</t>
+          <t>141124</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174731</t>
+          <t>177382</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,44%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>32932</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54114</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57888</t>
+          <t>56978</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76174</t>
+          <t>76228</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105709</t>
+          <t>105190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>358991</t>
+          <t>359659</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>402388</t>
+          <t>402182</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>374653</t>
+          <t>373723</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>421053</t>
+          <t>418506</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>747571</t>
+          <t>745526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>811049</t>
+          <t>809093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>223365</t>
+          <t>223314</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>264601</t>
+          <t>263770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>238411</t>
+          <t>242236</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>283920</t>
+          <t>286961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>472162</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533903</t>
+          <t>533286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72452</t>
+          <t>73045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101619</t>
+          <t>102445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>80972</t>
+          <t>80006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>110794</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161727</t>
+          <t>163777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>200764</t>
+          <t>204858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107269</t>
+          <t>106243</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120885</t>
+          <t>119948</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119388</t>
+          <t>120203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133716</t>
+          <t>133812</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231375</t>
+          <t>231234</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>251506</t>
+          <t>250493</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25083</t>
+          <t>24249</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11160</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25112</t>
+          <t>23838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>44798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9841</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126359</t>
+          <t>125790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147536</t>
+          <t>147041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146896</t>
+          <t>146469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>168291</t>
+          <t>167878</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277237</t>
+          <t>278264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>308087</t>
+          <t>309469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>48073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68676</t>
+          <t>68590</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39709</t>
+          <t>39824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59244</t>
+          <t>59562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94631</t>
+          <t>94413</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>123507</t>
+          <t>122490</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17518</t>
+          <t>18294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>25059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81943</t>
+          <t>82777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100877</t>
+          <t>101408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>86892</t>
+          <t>86244</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>107837</t>
+          <t>107040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>176518</t>
+          <t>175332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203341</t>
+          <t>203329</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36533</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54266</t>
+          <t>52376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74913</t>
+          <t>75452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99571</t>
+          <t>100585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26974</t>
+          <t>27799</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>18824</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34021</t>
+          <t>34498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36856</t>
+          <t>35949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56955</t>
+          <t>57568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102827</t>
+          <t>104573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127666</t>
+          <t>128820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98678</t>
+          <t>100031</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>122670</t>
+          <t>122492</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>212379</t>
+          <t>210659</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>244884</t>
+          <t>245931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47263</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70297</t>
+          <t>69402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52525</t>
+          <t>52666</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74273</t>
+          <t>74070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106229</t>
+          <t>106388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>136838</t>
+          <t>137565</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>23362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41192</t>
+          <t>40530</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23789</t>
+          <t>23703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>40858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51876</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75850</t>
+          <t>74716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>478984</t>
+          <t>479318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>472449</t>
+          <t>470904</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>515004</t>
+          <t>513778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924459</t>
+          <t>924272</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>983019</t>
+          <t>981435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>160046</t>
+          <t>158543</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>196175</t>
+          <t>197663</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>154001</t>
+          <t>156565</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>192618</t>
+          <t>193426</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>325908</t>
+          <t>324861</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>379028</t>
+          <t>378203</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,15%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>79214</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>63987</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92369</t>
+          <t>91419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124306</t>
+          <t>124477</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>162039</t>
+          <t>159978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100206</t>
+          <t>99320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110742</t>
+          <t>110623</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>124034</t>
+          <t>123402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135366</t>
+          <t>134904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228226</t>
+          <t>227236</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243846</t>
+          <t>243368</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4649</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>15045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9662</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>23550</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1255</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>140740</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159977</t>
+          <t>159762</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>202508</t>
+          <t>203199</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224475</t>
+          <t>224529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>350094</t>
+          <t>350468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>379782</t>
+          <t>378729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30932</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18206</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>36002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>38096</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>60686</t>
+          <t>61110</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24631</t>
+          <t>24896</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22648</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22564</t>
+          <t>22841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>41873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77948</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>159449</t>
+          <t>159806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119521</t>
+          <t>119597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147067</t>
+          <t>145934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>204916</t>
+          <t>197383</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296094</t>
+          <t>295239</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107771</t>
+          <t>106075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>50418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54374</t>
+          <t>54579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155361</t>
+          <t>161818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>43,07%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>8766</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>23262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34427</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86415</t>
+          <t>85459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>107611</t>
+          <t>107847</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89691</t>
+          <t>90792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114461</t>
+          <t>114042</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182181</t>
+          <t>185345</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>213574</t>
+          <t>217419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35008</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54116</t>
+          <t>54075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31072</t>
+          <t>31327</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51255</t>
+          <t>50480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69450</t>
+          <t>71131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97190</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>28606</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52591</t>
+          <t>52014</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77468</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>423296</t>
+          <t>410265</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>517636</t>
+          <t>517139</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558493</t>
+          <t>558039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605025</t>
+          <t>605183</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1005769</t>
+          <t>999638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1107058</t>
+          <t>1106032</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94219</t>
+          <t>91954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194047</t>
+          <t>204289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>91371</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130986</t>
+          <t>130487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>303754</t>
+          <t>307113</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42850</t>
+          <t>43018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66454</t>
+          <t>66814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>54324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105277</t>
+          <t>106374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143872</t>
+          <t>143721</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A07-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101085</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>90100</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>110111</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>92637</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>83616</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>102391</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>82832</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>101409</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>66,47%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>101085</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>90940</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>110801</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180430</t>
+          <t>180088</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>207579</t>
+          <t>207315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44890</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36451</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56753</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>29,02%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>40223</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30137</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48825</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32024</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>49912</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,86%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44890</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>36173</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54761</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>29,02%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72000</t>
+          <t>72742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98340</t>
+          <t>98878</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8708</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14809</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>6497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11618</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11661</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,66%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4746</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>14316</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>122497</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>110848</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>134360</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,73%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>60,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>113596</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>102089</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>124312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>102365</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>124054</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>55,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>60,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>122497</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>110610</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>135676</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219347</t>
+          <t>218968</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>252637</t>
+          <t>252811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82738</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>71437</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>93190</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>36,96%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>75143</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>64863</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>86080</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>64393</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>85825</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>36,41%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82738</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>70013</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>95416</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>36,96%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>140426</t>
+          <t>142944</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>173003</t>
+          <t>176155</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18600</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12602</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>26541</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17619</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11621</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24462</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12241</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>24872</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,54%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18600</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12197</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25557</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27738</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>46349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>87708</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77413</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>97038</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>52,65%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>46,47%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>58,25%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>90715</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>80599</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>100154</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>80777</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>100213</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>58,62%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>52,08%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>87708</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77805</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>98165</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>164868</t>
+          <t>164058</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>192527</t>
+          <t>192987</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,06%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56611</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47253</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66549</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,95%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>45338</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>36193</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54596</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36945</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55591</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>29,3%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>23,39%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>56611</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47561</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66531</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89797</t>
+          <t>88303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115730</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22273</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15977</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31091</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18696</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12772</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25614</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13278</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25549</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,08%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>22273</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15938</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>30280</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>51627</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166592</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>154749</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>154749</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>154749</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>166592</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>85337</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>73897</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>98205</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>35,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>84101</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>72214</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>97790</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71723</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>95989</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,14%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>85337</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>73936</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>97192</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,95%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151796</t>
+          <t>152898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185610</t>
+          <t>187940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,97%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>76712</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>64602</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88409</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>31,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>81953</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>68600</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>93261</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>70550</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>93800</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,11%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>76712</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>65616</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>88692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>141124</t>
+          <t>142263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>177382</t>
+          <t>175124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46347</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37462</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>57916</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>27,79%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43477</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>32932</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>54630</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>34116</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>53674</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>20,75%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>15,72%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>26,07%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46347</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>37016</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>56978</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76228</t>
+          <t>76489</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105190</t>
+          <t>105258</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>209532</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>396627</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>372837</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>417410</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>52,64%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>55,4%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>381050</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>359659</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>402182</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>360552</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>404369</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>53,67%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>56,65%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>396627</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>373723</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>418506</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>52,64%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>745526</t>
+          <t>747006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>809093</t>
+          <t>807229</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,16%</t>
         </is>
       </c>
     </row>
@@ -2659,72 +2659,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>260952</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>239795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>282585</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>34,63%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>348</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>242657</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>223314</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>263770</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>219620</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>262769</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>34,18%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>260952</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>242236</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>286961</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>472162</t>
+          <t>476942</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>533286</t>
+          <t>534677</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>95928</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>81296</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>111853</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>86289</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>73045</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>102445</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>73036</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>100948</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>12,15%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>10,29%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>95928</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>80006</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>111102</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163777</t>
+          <t>161806</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204858</t>
+          <t>203673</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1023</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>709996</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>127495</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>119834</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>133919</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,5%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,86%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>114454</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>106243</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119948</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>106462</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>120357</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>85,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>127495</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>120203</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>133812</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>231234</t>
+          <t>231516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250493</t>
+          <t>251537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17170</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11214</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24794</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>17103</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11664</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24249</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11943</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25102</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>12,79%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17170</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11314</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23838</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>43996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6905</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2150</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5862</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>1,61%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2734</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6959</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>147398</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>147398</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>147398</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>147398</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>147398</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>147398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>157647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145589</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>168604</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,27%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,89%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>136707</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>125790</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>147041</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>124128</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>146411</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,14%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>157647</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>146469</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>167878</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,27%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278264</t>
+          <t>277420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>309469</t>
+          <t>309593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,82%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49172</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38479</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>59170</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,15%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,37%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>58384</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>48073</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>68590</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>48776</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>69734</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>28,25%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>33,18%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49172</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>39824</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>59562</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>21,92%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>94413</t>
+          <t>93931</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122490</t>
+          <t>121125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,1%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17540</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11698</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25144</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11613</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7197</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18294</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7052</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17540</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11528</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25059</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21688</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38095</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>206703</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>206703</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>206703</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>97361</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>87202</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>107807</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>58,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>52,32%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>64,68%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>91695</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>82777</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>101408</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>81912</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>100324</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>59,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>97361</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86244</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>107040</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>175332</t>
+          <t>174582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>203329</t>
+          <t>202058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>43577</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>34128</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52627</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43898</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35524</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>52376</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>36120</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53603</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,24%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>43577</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>34989</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53722</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75452</t>
+          <t>75510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100585</t>
+          <t>101428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25735</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18057</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>19834</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14180</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27799</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>13769</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26702</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>12,76%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>25735</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18824</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>34498</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>56333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155427</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155427</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155427</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>110984</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>123595</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>116286</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>104573</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>128820</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>104604</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>129340</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,38%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>110984</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>100031</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>122492</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210659</t>
+          <t>207695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245931</t>
+          <t>243345</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,07%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>63523</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>53279</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75758</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>36,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>58595</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47226</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>69402</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>47756</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>28,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>22,9%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>33,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>63523</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>52666</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>74070</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,88%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106388</t>
+          <t>106282</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>137565</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -4828,72 +4828,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31229</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23503</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>40779</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>19,82%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>31372</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23362</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>40530</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>23301</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>41816</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>15,21%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>31229</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23703</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>40858</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51497</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74716</t>
+          <t>75635</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>206253</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>206253</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>206253</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>493486</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>471451</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>514241</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>63,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>693</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>459140</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>437997</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>479318</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>439424</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>479630</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>65,4%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>62,38%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>68,27%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>493486</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>470904</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>513778</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>66,31%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>924272</t>
+          <t>922504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>981435</t>
+          <t>982155</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,91%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>173441</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>156287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>193765</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>23,31%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>177979</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>158543</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>197663</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>160443</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>197385</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>25,35%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>22,58%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>173441</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>156565</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>193426</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324861</t>
+          <t>324986</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378203</t>
+          <t>377358</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>63623</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>90263</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>64969</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>52900</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>77780</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>53358</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>77694</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>9,25%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>63987</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>91419</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>10,38%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124477</t>
+          <t>124675</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>159978</t>
+          <t>162827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>744166</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>702089</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1064</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>744166</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>116684</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>110553</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121023</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,81%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>106252</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>99320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>110623</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>94,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>130382</t>
+          <t>109414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123402</t>
+          <t>103441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134904</t>
+          <t>114033</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>236636</t>
+          <t>226098</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227236</t>
+          <t>217617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243368</t>
+          <t>232658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11655</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8969</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15045</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23550</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -5972,72 +5972,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1078</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7205</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6004</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>342</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,22 +6047,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6202,72 +6202,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198374</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>185618</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>208015</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>150985</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>140740</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>159762</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>79,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>214699</t>
+          <t>144944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203199</t>
+          <t>134699</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>224529</t>
+          <t>154143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>365685</t>
+          <t>343318</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>350468</t>
+          <t>329008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>378729</t>
+          <t>356827</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>25355</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17748</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35637</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7,48%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15,02%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>22586</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>15803</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>30520</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26242</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18065</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>48828</t>
+          <t>47720</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38096</t>
+          <t>37411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61110</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13477</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8041</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>21428</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16940</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>11234</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24896</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>25049</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22841</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41873</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>122923</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>110292</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>133743</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>73,02%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>65,52%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>79,45%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>134219</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77092</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>159806</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>70,49%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>40,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>83,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134218</t>
+          <t>125056</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>119597</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145934</t>
+          <t>132905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>268438</t>
+          <t>247979</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>197383</t>
+          <t>232333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>295239</t>
+          <t>262432</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32986</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23790</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46692</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>19,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>46455</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19381</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>106075</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26133</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50418</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>83147</t>
+          <t>55386</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54579</t>
+          <t>43155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>161818</t>
+          <t>70894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12432</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7381</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9727</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4725</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>16800</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14376</t>
+          <t>9594</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23262</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34112</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94742</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83316</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>105825</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>62,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>97308</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>85459</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>107847</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>58,43%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>94835</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>90792</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114042</t>
+          <t>106379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>199746</t>
+          <t>189577</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185345</t>
+          <t>173584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217419</t>
+          <t>204966</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>61,17%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>38344</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29340</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>49093</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>22,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>17,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>29,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>43603</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>34698</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>54075</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>26,18%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40004</t>
+          <t>45363</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>35912</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50480</t>
+          <t>55963</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>83607</t>
+          <t>83708</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71131</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>97840</t>
+          <t>98675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>35333</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26636</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>25634</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18295</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28606</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>35619</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>63488</t>
+          <t>61783</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52014</t>
+          <t>50506</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77054</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>748</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>532723</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>511552</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>554024</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>76,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>79,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>488765</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>410265</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>517139</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>73,53%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>61,72%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>748</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>581738</t>
+          <t>474248</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558039</t>
+          <t>454972</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>605183</t>
+          <t>492195</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1070503</t>
+          <t>1006971</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>999638</t>
+          <t>976782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1106032</t>
+          <t>1034906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>102875</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>85200</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>121560</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>14,7%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>121613</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>91954</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>204289</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>18,29%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>30,73%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>109682</t>
+          <t>99667</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91371</t>
+          <t>85042</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130487</t>
+          <t>117071</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>231295</t>
+          <t>202542</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>177443</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>307113</t>
+          <t>227125</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>64274</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>51615</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>79534</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>54360</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>43018</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>66814</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,05%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69608</t>
+          <t>55267</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>43313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85544</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>103289</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143721</t>
+          <t>141051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
